--- a/AI_Scores.xlsx
+++ b/AI_Scores.xlsx
@@ -4,15 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000" tabRatio="500" firstSheet="1" activeTab="5"/>
+    <workbookView windowWidth="22188" windowHeight="9000" tabRatio="500" firstSheet="4" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="TP2" sheetId="1" r:id="rId1"/>
     <sheet name="TP4" sheetId="2" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" r:id="rId3"/>
-    <sheet name="Model Averages" sheetId="4" r:id="rId4"/>
-    <sheet name="Prompt numbers" sheetId="5" r:id="rId5"/>
-    <sheet name="File Scores" sheetId="6" r:id="rId6"/>
+    <sheet name="TP5" sheetId="7" r:id="rId3"/>
+    <sheet name="TP8" sheetId="8" r:id="rId4"/>
+    <sheet name="Summary" sheetId="3" r:id="rId5"/>
+    <sheet name="Model Averages" sheetId="4" r:id="rId6"/>
+    <sheet name="Prompt numbers" sheetId="5" r:id="rId7"/>
+    <sheet name="File Scores" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="51">
   <si>
     <t>Model</t>
   </si>
@@ -142,6 +144,15 @@
     <t>tableau_supprimer</t>
   </si>
   <si>
+    <t>scenario_stock / stocks_materiel</t>
+  </si>
+  <si>
+    <t>vecteurs_creux</t>
+  </si>
+  <si>
+    <t>exemple_vecteurs_creux</t>
+  </si>
+  <si>
     <t>TP</t>
   </si>
   <si>
@@ -158,6 +169,12 @@
   </si>
   <si>
     <t>TP4</t>
+  </si>
+  <si>
+    <t>TP5</t>
+  </si>
+  <si>
+    <t>TP8</t>
   </si>
   <si>
     <t>Total Prompts</t>
@@ -209,14 +226,14 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
@@ -871,7 +888,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -888,23 +905,35 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2562,6 +2591,1152 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>TP5</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Model Averages'!$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Gemini</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1" forceAA="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Model Averages'!$C$8:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1" c:formatCode="0.00">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2" c:formatCode="0.00">
+                  <c:v>4.25</c:v>
+                </c:pt>
+                <c:pt idx="3" c:formatCode="0.00">
+                  <c:v>4.62</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Model Averages'!$B$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Claude</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1" forceAA="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Model Averages'!$C$9:$F$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1" c:formatCode="0.00">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2" c:formatCode="0.00">
+                  <c:v>4.25</c:v>
+                </c:pt>
+                <c:pt idx="3" c:formatCode="0.00">
+                  <c:v>4.62</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Model Averages'!$B$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CoPilot</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1" forceAA="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Model Averages'!$C$10:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1" c:formatCode="0.00">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2" c:formatCode="0.00">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="3" c:formatCode="0.00">
+                  <c:v>4.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="260"/>
+        <c:overlap val="-32"/>
+        <c:axId val="212802079"/>
+        <c:axId val="56397840"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="212802079"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="56397840"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="56397840"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="212802079"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+          <a:alpha val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="zh-CN" sz="900">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+          <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+          <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+          <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+        </a:defRPr>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:clrMapOvr bg1="lt1" tx1="dk1" bg2="lt2" tx2="dk2" accent1="accent1" accent2="accent2" accent3="accent3" accent4="accent4" accent5="accent5" accent6="accent6" hlink="hlink" folHlink="folHlink"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>TP8</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Model Averages'!$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Gemini</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1" forceAA="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Model Averages'!$C$11:$F$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1" c:formatCode="0.00">
+                  <c:v>4.62</c:v>
+                </c:pt>
+                <c:pt idx="2" c:formatCode="0.00">
+                  <c:v>3.62</c:v>
+                </c:pt>
+                <c:pt idx="3" c:formatCode="0.00">
+                  <c:v>4.12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Model Averages'!$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Claude</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1" forceAA="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Model Averages'!$C$12:$F$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1" c:formatCode="0.00">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2" c:formatCode="0.00">
+                  <c:v>4.67</c:v>
+                </c:pt>
+                <c:pt idx="3" c:formatCode="0.00">
+                  <c:v>4.83</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Model Averages'!$B$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CoPilot</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1" forceAA="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                    <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Model Averages'!$C$13:$F$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1" c:formatCode="0.00">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2" c:formatCode="0.00">
+                  <c:v>4.25</c:v>
+                </c:pt>
+                <c:pt idx="3" c:formatCode="0.00">
+                  <c:v>4.12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="260"/>
+        <c:overlap val="-32"/>
+        <c:axId val="85459719"/>
+        <c:axId val="92069758"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="85459719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="92069758"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="92069758"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="85459719"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+          <a:alpha val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="zh-CN" sz="900">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+          <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+          <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+          <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+        </a:defRPr>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:clrMapOvr bg1="lt1" tx1="dk1" bg2="lt2" tx2="dk2" accent1="accent1" accent2="accent2" accent3="accent3" accent4="accent4" accent5="accent5" accent6="accent6" hlink="hlink" folHlink="folHlink"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:ea typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:cs typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:sym typeface="Microsoft YaHei" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
               <a:t>Prompt par fichier</a:t>
             </a:r>
             <a:endParaRPr lang="en-US" altLang="zh-CN"/>
@@ -2669,9 +3844,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Prompt numbers'!$B$2:$B$14</c:f>
+              <c:f>'Prompt numbers'!$B$2:$B$17</c:f>
               <c:strCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>permuter_caracteres</c:v>
                 </c:pt>
@@ -2710,16 +3885,25 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>tableau_supprimer</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>scenario_stock / stocks_materiel</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>vecteurs_creux</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>exemple_vecteurs_creux</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Prompt numbers'!$C$2:$C$14</c:f>
+              <c:f>'Prompt numbers'!$C$2:$C$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -2758,6 +3942,15 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2847,9 +4040,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Prompt numbers'!$B$2:$B$14</c:f>
+              <c:f>'Prompt numbers'!$B$2:$B$17</c:f>
               <c:strCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>permuter_caracteres</c:v>
                 </c:pt>
@@ -2888,16 +4081,25 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>tableau_supprimer</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>scenario_stock / stocks_materiel</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>vecteurs_creux</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>exemple_vecteurs_creux</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Prompt numbers'!$D$2:$D$14</c:f>
+              <c:f>'Prompt numbers'!$D$2:$D$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -2936,6 +4138,15 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3025,9 +4236,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Prompt numbers'!$B$2:$B$14</c:f>
+              <c:f>'Prompt numbers'!$B$2:$B$17</c:f>
               <c:strCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>permuter_caracteres</c:v>
                 </c:pt>
@@ -3066,16 +4277,25 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>tableau_supprimer</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>scenario_stock / stocks_materiel</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>vecteurs_creux</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>exemple_vecteurs_creux</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Prompt numbers'!$E$2:$E$14</c:f>
+              <c:f>'Prompt numbers'!$E$2:$E$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -3114,6 +4334,15 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3325,7 +4554,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="zh-CN"/>
@@ -3469,9 +4698,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'File Scores'!$C$2:$C$14</c:f>
+              <c:f>'File Scores'!$C$2:$C$17</c:f>
               <c:strCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>permuter_caracteres</c:v>
                 </c:pt>
@@ -3510,16 +4739,25 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>tableau_supprimer</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>scenario_stock / stocks_materiel</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>vecteurs_creux</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>exemple_vecteurs_creux</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'File Scores'!$D$2:$D$14</c:f>
+              <c:f>'File Scores'!$D$2:$D$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -3558,6 +4796,15 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="13" c:formatCode="0.00">
+                  <c:v>4.62</c:v>
+                </c:pt>
+                <c:pt idx="14" c:formatCode="0.00">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="15" c:formatCode="0.00">
+                  <c:v>3.83</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3647,9 +4894,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'File Scores'!$C$2:$C$14</c:f>
+              <c:f>'File Scores'!$C$2:$C$17</c:f>
               <c:strCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>permuter_caracteres</c:v>
                 </c:pt>
@@ -3688,16 +4935,25 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>tableau_supprimer</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>scenario_stock / stocks_materiel</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>vecteurs_creux</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>exemple_vecteurs_creux</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'File Scores'!$E$2:$E$14</c:f>
+              <c:f>'File Scores'!$E$2:$E$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -3736,6 +4992,15 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="13" c:formatCode="0.00">
+                  <c:v>4.62</c:v>
+                </c:pt>
+                <c:pt idx="14" c:formatCode="0.00">
+                  <c:v>4.75</c:v>
+                </c:pt>
+                <c:pt idx="15" c:formatCode="0.00">
+                  <c:v>4.88</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3825,9 +5090,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'File Scores'!$C$2:$C$14</c:f>
+              <c:f>'File Scores'!$C$2:$C$17</c:f>
               <c:strCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>permuter_caracteres</c:v>
                 </c:pt>
@@ -3866,16 +5131,25 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>tableau_supprimer</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>scenario_stock / stocks_materiel</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>vecteurs_creux</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>exemple_vecteurs_creux</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'File Scores'!$F$2:$F$14</c:f>
+              <c:f>'File Scores'!$F$2:$F$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>4.5</c:v>
                 </c:pt>
@@ -3913,6 +5187,15 @@
                   <c:v>4.25</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="13" c:formatCode="0.00">
+                  <c:v>4.25</c:v>
+                </c:pt>
+                <c:pt idx="14" c:formatCode="0.00">
+                  <c:v>4.25</c:v>
+                </c:pt>
+                <c:pt idx="15" c:formatCode="0.00">
                   <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
@@ -4285,6 +5568,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10002">
   <cs:axisTitle>
@@ -6325,20 +7688,1040 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10002">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10002">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>643255</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:colOff>620395</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6346,7 +8729,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="205740" y="1647825"/>
+        <a:off x="182880" y="3362325"/>
         <a:ext cx="4826635" cy="2743200"/>
       </xdr:xfrm>
       <a:graphic>
@@ -6361,14 +8744,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>586740</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6376,12 +8759,72 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4975860" y="1655445"/>
+        <a:off x="4975860" y="3369945"/>
         <a:ext cx="4826635" cy="2743200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>138430</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>33020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>575945</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>33020</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1" descr="7b0a202020202263686172745265734964223a202234363130333534220a7d0a"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="138430" y="6237605"/>
+        <a:ext cx="4826635" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>726440</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>130175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>248285</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>130175</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2" descr="7b0a202020202263686172745265734964223a202234363130333534220a7d0a"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="5115560" y="6334760"/>
+        <a:ext cx="4828540" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -7612,6 +10055,494 @@
 </a:themeOverride>
 </file>
 
+<file path=xl/theme/themeOverride5.xml><?xml version="1.0" encoding="utf-8"?>
+<a:themeOverride xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <a:clrScheme name="WPS">
+    <a:dk1>
+      <a:sysClr val="windowText" lastClr="000000"/>
+    </a:dk1>
+    <a:lt1>
+      <a:sysClr val="window" lastClr="FFFFFF"/>
+    </a:lt1>
+    <a:dk2>
+      <a:srgbClr val="44546A"/>
+    </a:dk2>
+    <a:lt2>
+      <a:srgbClr val="E7E6E6"/>
+    </a:lt2>
+    <a:accent1>
+      <a:srgbClr val="4874CB"/>
+    </a:accent1>
+    <a:accent2>
+      <a:srgbClr val="EE822F"/>
+    </a:accent2>
+    <a:accent3>
+      <a:srgbClr val="F2BA02"/>
+    </a:accent3>
+    <a:accent4>
+      <a:srgbClr val="75BD42"/>
+    </a:accent4>
+    <a:accent5>
+      <a:srgbClr val="30C0B4"/>
+    </a:accent5>
+    <a:accent6>
+      <a:srgbClr val="E54C5E"/>
+    </a:accent6>
+    <a:hlink>
+      <a:srgbClr val="0026E5"/>
+    </a:hlink>
+    <a:folHlink>
+      <a:srgbClr val="7E1FAD"/>
+    </a:folHlink>
+  </a:clrScheme>
+  <a:fontScheme name="WPS">
+    <a:majorFont>
+      <a:latin typeface="Calibri Light"/>
+      <a:ea typeface=""/>
+      <a:cs typeface=""/>
+      <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+      <a:font script="Hang" typeface="맑은 고딕"/>
+      <a:font script="Hans" typeface="宋体"/>
+      <a:font script="Hant" typeface="新細明體"/>
+      <a:font script="Arab" typeface="Times New Roman"/>
+      <a:font script="Hebr" typeface="Times New Roman"/>
+      <a:font script="Thai" typeface="Tahoma"/>
+      <a:font script="Ethi" typeface="Nyala"/>
+      <a:font script="Beng" typeface="Vrinda"/>
+      <a:font script="Gujr" typeface="Shruti"/>
+      <a:font script="Khmr" typeface="MoolBoran"/>
+      <a:font script="Knda" typeface="Tunga"/>
+      <a:font script="Guru" typeface="Raavi"/>
+      <a:font script="Cans" typeface="Euphemia"/>
+      <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+      <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+      <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+      <a:font script="Thaa" typeface="MV Boli"/>
+      <a:font script="Deva" typeface="Mangal"/>
+      <a:font script="Telu" typeface="Gautami"/>
+      <a:font script="Taml" typeface="Latha"/>
+      <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+      <a:font script="Orya" typeface="Kalinga"/>
+      <a:font script="Mlym" typeface="Kartika"/>
+      <a:font script="Laoo" typeface="DokChampa"/>
+      <a:font script="Sinh" typeface="Iskoola Pota"/>
+      <a:font script="Mong" typeface="Mongolian Baiti"/>
+      <a:font script="Viet" typeface="Times New Roman"/>
+      <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      <a:font script="Geor" typeface="Sylfaen"/>
+    </a:majorFont>
+    <a:minorFont>
+      <a:latin typeface="Calibri"/>
+      <a:ea typeface=""/>
+      <a:cs typeface=""/>
+      <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+      <a:font script="Hang" typeface="맑은 고딕"/>
+      <a:font script="Hans" typeface="宋体"/>
+      <a:font script="Hant" typeface="新細明體"/>
+      <a:font script="Arab" typeface="Arial"/>
+      <a:font script="Hebr" typeface="Arial"/>
+      <a:font script="Thai" typeface="Tahoma"/>
+      <a:font script="Ethi" typeface="Nyala"/>
+      <a:font script="Beng" typeface="Vrinda"/>
+      <a:font script="Gujr" typeface="Shruti"/>
+      <a:font script="Khmr" typeface="DaunPenh"/>
+      <a:font script="Knda" typeface="Tunga"/>
+      <a:font script="Guru" typeface="Raavi"/>
+      <a:font script="Cans" typeface="Euphemia"/>
+      <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+      <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+      <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+      <a:font script="Thaa" typeface="MV Boli"/>
+      <a:font script="Deva" typeface="Mangal"/>
+      <a:font script="Telu" typeface="Gautami"/>
+      <a:font script="Taml" typeface="Latha"/>
+      <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+      <a:font script="Orya" typeface="Kalinga"/>
+      <a:font script="Mlym" typeface="Kartika"/>
+      <a:font script="Laoo" typeface="DokChampa"/>
+      <a:font script="Sinh" typeface="Iskoola Pota"/>
+      <a:font script="Mong" typeface="Mongolian Baiti"/>
+      <a:font script="Viet" typeface="Arial"/>
+      <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      <a:font script="Geor" typeface="Sylfaen"/>
+    </a:minorFont>
+  </a:fontScheme>
+  <a:fmtScheme name="WPS">
+    <a:fillStyleLst>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:lumOff val="17500"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="2700000" scaled="0"/>
+      </a:gradFill>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:hueOff val="-2520000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="2700000" scaled="0"/>
+      </a:gradFill>
+    </a:fillStyleLst>
+    <a:lnStyleLst>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="solid"/>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="solid"/>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:hueOff val="-4200000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="2700000" scaled="1"/>
+        </a:gradFill>
+        <a:prstDash val="solid"/>
+        <a:miter lim="800000"/>
+      </a:ln>
+    </a:lnStyleLst>
+    <a:effectStyleLst>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:schemeClr val="phClr">
+              <a:alpha val="60000"/>
+            </a:schemeClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </a:effectStyle>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+        </a:effectLst>
+      </a:effectStyle>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="63000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </a:effectStyle>
+    </a:effectStyleLst>
+    <a:bgFillStyleLst>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:tint val="95000"/>
+          <a:satMod val="170000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:gradFill rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:tint val="93000"/>
+              <a:satMod val="150000"/>
+              <a:shade val="98000"/>
+              <a:lumMod val="102000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="50000">
+            <a:schemeClr val="phClr">
+              <a:tint val="98000"/>
+              <a:satMod val="130000"/>
+              <a:shade val="90000"/>
+              <a:lumMod val="103000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:shade val="63000"/>
+              <a:satMod val="120000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </a:bgFillStyleLst>
+  </a:fmtScheme>
+</a:themeOverride>
+</file>
+
+<file path=xl/theme/themeOverride6.xml><?xml version="1.0" encoding="utf-8"?>
+<a:themeOverride xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <a:clrScheme name="WPS">
+    <a:dk1>
+      <a:sysClr val="windowText" lastClr="000000"/>
+    </a:dk1>
+    <a:lt1>
+      <a:sysClr val="window" lastClr="FFFFFF"/>
+    </a:lt1>
+    <a:dk2>
+      <a:srgbClr val="44546A"/>
+    </a:dk2>
+    <a:lt2>
+      <a:srgbClr val="E7E6E6"/>
+    </a:lt2>
+    <a:accent1>
+      <a:srgbClr val="4874CB"/>
+    </a:accent1>
+    <a:accent2>
+      <a:srgbClr val="EE822F"/>
+    </a:accent2>
+    <a:accent3>
+      <a:srgbClr val="F2BA02"/>
+    </a:accent3>
+    <a:accent4>
+      <a:srgbClr val="75BD42"/>
+    </a:accent4>
+    <a:accent5>
+      <a:srgbClr val="30C0B4"/>
+    </a:accent5>
+    <a:accent6>
+      <a:srgbClr val="E54C5E"/>
+    </a:accent6>
+    <a:hlink>
+      <a:srgbClr val="0026E5"/>
+    </a:hlink>
+    <a:folHlink>
+      <a:srgbClr val="7E1FAD"/>
+    </a:folHlink>
+  </a:clrScheme>
+  <a:fontScheme name="WPS">
+    <a:majorFont>
+      <a:latin typeface="Calibri Light"/>
+      <a:ea typeface=""/>
+      <a:cs typeface=""/>
+      <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+      <a:font script="Hang" typeface="맑은 고딕"/>
+      <a:font script="Hans" typeface="宋体"/>
+      <a:font script="Hant" typeface="新細明體"/>
+      <a:font script="Arab" typeface="Times New Roman"/>
+      <a:font script="Hebr" typeface="Times New Roman"/>
+      <a:font script="Thai" typeface="Tahoma"/>
+      <a:font script="Ethi" typeface="Nyala"/>
+      <a:font script="Beng" typeface="Vrinda"/>
+      <a:font script="Gujr" typeface="Shruti"/>
+      <a:font script="Khmr" typeface="MoolBoran"/>
+      <a:font script="Knda" typeface="Tunga"/>
+      <a:font script="Guru" typeface="Raavi"/>
+      <a:font script="Cans" typeface="Euphemia"/>
+      <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+      <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+      <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+      <a:font script="Thaa" typeface="MV Boli"/>
+      <a:font script="Deva" typeface="Mangal"/>
+      <a:font script="Telu" typeface="Gautami"/>
+      <a:font script="Taml" typeface="Latha"/>
+      <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+      <a:font script="Orya" typeface="Kalinga"/>
+      <a:font script="Mlym" typeface="Kartika"/>
+      <a:font script="Laoo" typeface="DokChampa"/>
+      <a:font script="Sinh" typeface="Iskoola Pota"/>
+      <a:font script="Mong" typeface="Mongolian Baiti"/>
+      <a:font script="Viet" typeface="Times New Roman"/>
+      <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      <a:font script="Geor" typeface="Sylfaen"/>
+    </a:majorFont>
+    <a:minorFont>
+      <a:latin typeface="Calibri"/>
+      <a:ea typeface=""/>
+      <a:cs typeface=""/>
+      <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+      <a:font script="Hang" typeface="맑은 고딕"/>
+      <a:font script="Hans" typeface="宋体"/>
+      <a:font script="Hant" typeface="新細明體"/>
+      <a:font script="Arab" typeface="Arial"/>
+      <a:font script="Hebr" typeface="Arial"/>
+      <a:font script="Thai" typeface="Tahoma"/>
+      <a:font script="Ethi" typeface="Nyala"/>
+      <a:font script="Beng" typeface="Vrinda"/>
+      <a:font script="Gujr" typeface="Shruti"/>
+      <a:font script="Khmr" typeface="DaunPenh"/>
+      <a:font script="Knda" typeface="Tunga"/>
+      <a:font script="Guru" typeface="Raavi"/>
+      <a:font script="Cans" typeface="Euphemia"/>
+      <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+      <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+      <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+      <a:font script="Thaa" typeface="MV Boli"/>
+      <a:font script="Deva" typeface="Mangal"/>
+      <a:font script="Telu" typeface="Gautami"/>
+      <a:font script="Taml" typeface="Latha"/>
+      <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+      <a:font script="Orya" typeface="Kalinga"/>
+      <a:font script="Mlym" typeface="Kartika"/>
+      <a:font script="Laoo" typeface="DokChampa"/>
+      <a:font script="Sinh" typeface="Iskoola Pota"/>
+      <a:font script="Mong" typeface="Mongolian Baiti"/>
+      <a:font script="Viet" typeface="Arial"/>
+      <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      <a:font script="Geor" typeface="Sylfaen"/>
+    </a:minorFont>
+  </a:fontScheme>
+  <a:fmtScheme name="WPS">
+    <a:fillStyleLst>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:lumOff val="17500"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="2700000" scaled="0"/>
+      </a:gradFill>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:hueOff val="-2520000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="2700000" scaled="0"/>
+      </a:gradFill>
+    </a:fillStyleLst>
+    <a:lnStyleLst>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="solid"/>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="solid"/>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:hueOff val="-4200000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="2700000" scaled="1"/>
+        </a:gradFill>
+        <a:prstDash val="solid"/>
+        <a:miter lim="800000"/>
+      </a:ln>
+    </a:lnStyleLst>
+    <a:effectStyleLst>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:schemeClr val="phClr">
+              <a:alpha val="60000"/>
+            </a:schemeClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </a:effectStyle>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+        </a:effectLst>
+      </a:effectStyle>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="63000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </a:effectStyle>
+    </a:effectStyleLst>
+    <a:bgFillStyleLst>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:tint val="95000"/>
+          <a:satMod val="170000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:gradFill rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:tint val="93000"/>
+              <a:satMod val="150000"/>
+              <a:shade val="98000"/>
+              <a:lumMod val="102000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="50000">
+            <a:schemeClr val="phClr">
+              <a:tint val="98000"/>
+              <a:satMod val="130000"/>
+              <a:shade val="90000"/>
+              <a:lumMod val="103000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:shade val="63000"/>
+              <a:satMod val="120000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </a:bgFillStyleLst>
+  </a:fmtScheme>
+</a:themeOverride>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -7626,61 +10557,61 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:19">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="7" t="s">
+      <c r="F1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="S1" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -7688,58 +10619,58 @@
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="11">
         <v>2</v>
       </c>
-      <c r="D2" s="9">
-        <v>5</v>
-      </c>
-      <c r="E2" s="9">
-        <v>5</v>
-      </c>
-      <c r="F2" s="8">
-        <v>5</v>
-      </c>
-      <c r="G2" s="8">
-        <v>5</v>
-      </c>
-      <c r="H2" s="8">
-        <v>5</v>
-      </c>
-      <c r="I2" s="8">
-        <v>5</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S2" s="11" t="s">
+      <c r="D2" s="7">
+        <v>5</v>
+      </c>
+      <c r="E2" s="7">
+        <v>5</v>
+      </c>
+      <c r="F2" s="11">
+        <v>5</v>
+      </c>
+      <c r="G2" s="11">
+        <v>5</v>
+      </c>
+      <c r="H2" s="11">
+        <v>5</v>
+      </c>
+      <c r="I2" s="11">
+        <v>5</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -7747,58 +10678,58 @@
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="11">
         <v>2</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="7">
         <v>4.75</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="7">
         <v>4.75</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="11">
         <v>4.5</v>
       </c>
-      <c r="G3" s="8">
-        <v>5</v>
-      </c>
-      <c r="H3" s="8">
-        <v>5</v>
-      </c>
-      <c r="I3" s="8">
+      <c r="G3" s="11">
+        <v>5</v>
+      </c>
+      <c r="H3" s="11">
+        <v>5</v>
+      </c>
+      <c r="I3" s="11">
         <v>4.5</v>
       </c>
-      <c r="J3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S3" s="11" t="s">
+      <c r="J3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S3" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -7806,58 +10737,58 @@
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="11">
         <v>2</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="7">
         <v>4.75</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="7">
         <v>4</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="11">
         <v>4.5</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="11">
         <v>4.5</v>
       </c>
-      <c r="H4" s="8">
-        <v>5</v>
-      </c>
-      <c r="I4" s="8">
+      <c r="H4" s="11">
+        <v>5</v>
+      </c>
+      <c r="I4" s="11">
         <v>3.5</v>
       </c>
-      <c r="J4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S4" s="11" t="s">
+      <c r="J4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S4" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -7865,58 +10796,58 @@
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="11">
         <v>2</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="7">
         <v>4.75</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="7">
         <v>4.75</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="11">
         <v>4.5</v>
       </c>
-      <c r="G5" s="8">
-        <v>5</v>
-      </c>
-      <c r="H5" s="8">
-        <v>5</v>
-      </c>
-      <c r="I5" s="8">
+      <c r="G5" s="11">
+        <v>5</v>
+      </c>
+      <c r="H5" s="11">
+        <v>5</v>
+      </c>
+      <c r="I5" s="11">
         <v>4.5</v>
       </c>
-      <c r="J5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S5" s="11" t="s">
+      <c r="J5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S5" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -7924,58 +10855,58 @@
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="11">
         <v>2</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="7">
         <v>4.75</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="7">
         <v>4.5</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="11">
         <v>4.5</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="11">
         <v>4.5</v>
       </c>
-      <c r="H6" s="8">
-        <v>5</v>
-      </c>
-      <c r="I6" s="8">
+      <c r="H6" s="11">
+        <v>5</v>
+      </c>
+      <c r="I6" s="11">
         <v>4.5</v>
       </c>
-      <c r="J6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S6" s="11" t="s">
+      <c r="J6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S6" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -7983,58 +10914,58 @@
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="11">
         <v>2</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="7">
         <v>4.75</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="7">
         <v>4.25</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="11">
         <v>4.5</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="11">
         <v>4.5</v>
       </c>
-      <c r="H7" s="8">
-        <v>5</v>
-      </c>
-      <c r="I7" s="8">
+      <c r="H7" s="11">
+        <v>5</v>
+      </c>
+      <c r="I7" s="11">
         <v>4</v>
       </c>
-      <c r="J7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S7" s="11" t="s">
+      <c r="J7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S7" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8042,58 +10973,58 @@
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="11">
         <v>2</v>
       </c>
-      <c r="D8" s="9">
-        <v>5</v>
-      </c>
-      <c r="E8" s="9">
-        <v>5</v>
-      </c>
-      <c r="F8" s="8">
-        <v>5</v>
-      </c>
-      <c r="G8" s="8">
-        <v>5</v>
-      </c>
-      <c r="H8" s="8">
-        <v>5</v>
-      </c>
-      <c r="I8" s="8">
-        <v>5</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S8" s="11" t="s">
+      <c r="D8" s="7">
+        <v>5</v>
+      </c>
+      <c r="E8" s="7">
+        <v>5</v>
+      </c>
+      <c r="F8" s="11">
+        <v>5</v>
+      </c>
+      <c r="G8" s="11">
+        <v>5</v>
+      </c>
+      <c r="H8" s="11">
+        <v>5</v>
+      </c>
+      <c r="I8" s="11">
+        <v>5</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S8" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8101,58 +11032,58 @@
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="11">
         <v>2</v>
       </c>
-      <c r="D9" s="9">
-        <v>5</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="D9" s="7">
+        <v>5</v>
+      </c>
+      <c r="E9" s="7">
         <v>4</v>
       </c>
-      <c r="F9" s="8">
-        <v>5</v>
-      </c>
-      <c r="G9" s="8">
+      <c r="F9" s="11">
+        <v>5</v>
+      </c>
+      <c r="G9" s="11">
         <v>4</v>
       </c>
-      <c r="H9" s="8">
-        <v>5</v>
-      </c>
-      <c r="I9" s="8">
+      <c r="H9" s="11">
+        <v>5</v>
+      </c>
+      <c r="I9" s="11">
         <v>4</v>
       </c>
-      <c r="J9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S9" s="11" t="s">
+      <c r="J9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S9" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8160,58 +11091,58 @@
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="11">
         <v>3</v>
       </c>
-      <c r="D10" s="9">
-        <v>5</v>
-      </c>
-      <c r="E10" s="9">
+      <c r="D10" s="7">
+        <v>5</v>
+      </c>
+      <c r="E10" s="7">
         <v>4.17</v>
       </c>
-      <c r="F10" s="8">
-        <v>5</v>
-      </c>
-      <c r="G10" s="8">
+      <c r="F10" s="11">
+        <v>5</v>
+      </c>
+      <c r="G10" s="11">
         <v>4</v>
       </c>
-      <c r="H10" s="8">
-        <v>5</v>
-      </c>
-      <c r="I10" s="8">
+      <c r="H10" s="11">
+        <v>5</v>
+      </c>
+      <c r="I10" s="11">
         <v>4</v>
       </c>
-      <c r="J10" s="8">
-        <v>5</v>
-      </c>
-      <c r="K10" s="8">
+      <c r="J10" s="11">
+        <v>5</v>
+      </c>
+      <c r="K10" s="11">
         <v>4.5</v>
       </c>
-      <c r="L10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S10" s="11" t="s">
+      <c r="L10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S10" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8219,58 +11150,58 @@
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="11">
         <v>3</v>
       </c>
-      <c r="D11" s="9">
-        <v>5</v>
-      </c>
-      <c r="E11" s="9">
+      <c r="D11" s="7">
+        <v>5</v>
+      </c>
+      <c r="E11" s="7">
         <v>3.67</v>
       </c>
-      <c r="F11" s="8">
-        <v>5</v>
-      </c>
-      <c r="G11" s="8">
+      <c r="F11" s="11">
+        <v>5</v>
+      </c>
+      <c r="G11" s="11">
         <v>2</v>
       </c>
-      <c r="H11" s="8">
-        <v>5</v>
-      </c>
-      <c r="I11" s="8">
+      <c r="H11" s="11">
+        <v>5</v>
+      </c>
+      <c r="I11" s="11">
         <v>4.5</v>
       </c>
-      <c r="J11" s="8">
-        <v>5</v>
-      </c>
-      <c r="K11" s="8">
+      <c r="J11" s="11">
+        <v>5</v>
+      </c>
+      <c r="K11" s="11">
         <v>4.5</v>
       </c>
-      <c r="L11" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P11" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q11" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R11" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S11" s="11" t="s">
+      <c r="L11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S11" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8278,58 +11209,58 @@
       <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="11">
         <v>2</v>
       </c>
-      <c r="D12" s="9">
-        <v>5</v>
-      </c>
-      <c r="E12" s="9">
-        <v>5</v>
-      </c>
-      <c r="F12" s="8">
-        <v>5</v>
-      </c>
-      <c r="G12" s="8">
-        <v>5</v>
-      </c>
-      <c r="H12" s="8">
-        <v>5</v>
-      </c>
-      <c r="I12" s="8">
-        <v>5</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S12" s="11" t="s">
+      <c r="D12" s="7">
+        <v>5</v>
+      </c>
+      <c r="E12" s="7">
+        <v>5</v>
+      </c>
+      <c r="F12" s="11">
+        <v>5</v>
+      </c>
+      <c r="G12" s="11">
+        <v>5</v>
+      </c>
+      <c r="H12" s="11">
+        <v>5</v>
+      </c>
+      <c r="I12" s="11">
+        <v>5</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S12" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8337,58 +11268,58 @@
       <c r="A13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="11">
         <v>2</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="7">
         <v>4.75</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="7">
         <v>4.75</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="11">
         <v>4.5</v>
       </c>
-      <c r="G13" s="8">
-        <v>5</v>
-      </c>
-      <c r="H13" s="8">
-        <v>5</v>
-      </c>
-      <c r="I13" s="8">
+      <c r="G13" s="11">
+        <v>5</v>
+      </c>
+      <c r="H13" s="11">
+        <v>5</v>
+      </c>
+      <c r="I13" s="11">
         <v>4.5</v>
       </c>
-      <c r="J13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S13" s="11" t="s">
+      <c r="J13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S13" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8396,58 +11327,58 @@
       <c r="A14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="11">
         <v>2</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="7">
         <v>4.75</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="7">
         <v>4</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="11">
         <v>4.5</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="11">
         <v>4.5</v>
       </c>
-      <c r="H14" s="8">
-        <v>5</v>
-      </c>
-      <c r="I14" s="8">
+      <c r="H14" s="11">
+        <v>5</v>
+      </c>
+      <c r="I14" s="11">
         <v>3.5</v>
       </c>
-      <c r="J14" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N14" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O14" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P14" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q14" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R14" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S14" s="11" t="s">
+      <c r="J14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S14" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8455,58 +11386,58 @@
       <c r="A15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="11">
         <v>2</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="7">
         <v>4.75</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="7">
         <v>4.75</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="11">
         <v>4.5</v>
       </c>
-      <c r="G15" s="8">
-        <v>5</v>
-      </c>
-      <c r="H15" s="8">
-        <v>5</v>
-      </c>
-      <c r="I15" s="8">
+      <c r="G15" s="11">
+        <v>5</v>
+      </c>
+      <c r="H15" s="11">
+        <v>5</v>
+      </c>
+      <c r="I15" s="11">
         <v>4.5</v>
       </c>
-      <c r="J15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S15" s="11" t="s">
+      <c r="J15" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P15" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R15" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S15" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8514,58 +11445,58 @@
       <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="11">
         <v>2</v>
       </c>
-      <c r="D16" s="9">
-        <v>5</v>
-      </c>
-      <c r="E16" s="9">
+      <c r="D16" s="7">
+        <v>5</v>
+      </c>
+      <c r="E16" s="7">
         <v>4.75</v>
       </c>
-      <c r="F16" s="8">
-        <v>5</v>
-      </c>
-      <c r="G16" s="8">
-        <v>5</v>
-      </c>
-      <c r="H16" s="8">
-        <v>5</v>
-      </c>
-      <c r="I16" s="8">
+      <c r="F16" s="11">
+        <v>5</v>
+      </c>
+      <c r="G16" s="11">
+        <v>5</v>
+      </c>
+      <c r="H16" s="11">
+        <v>5</v>
+      </c>
+      <c r="I16" s="11">
         <v>4.5</v>
       </c>
-      <c r="J16" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N16" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P16" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q16" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R16" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S16" s="11" t="s">
+      <c r="J16" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R16" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S16" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8573,58 +11504,58 @@
       <c r="A17" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="11">
         <v>2</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="7">
         <v>3</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="7">
         <v>4.75</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="11">
         <v>3</v>
       </c>
-      <c r="G17" s="8">
-        <v>5</v>
-      </c>
-      <c r="H17" s="8">
+      <c r="G17" s="11">
+        <v>5</v>
+      </c>
+      <c r="H17" s="11">
         <v>3</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="11">
         <v>4.5</v>
       </c>
-      <c r="J17" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L17" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N17" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O17" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P17" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q17" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R17" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S17" s="11" t="s">
+      <c r="J17" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P17" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q17" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R17" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S17" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8632,58 +11563,58 @@
       <c r="A18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="11">
         <v>2</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="7">
         <v>4</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="7">
         <v>4.75</v>
       </c>
-      <c r="F18" s="8">
-        <v>5</v>
-      </c>
-      <c r="G18" s="8">
-        <v>5</v>
-      </c>
-      <c r="H18" s="8">
+      <c r="F18" s="11">
+        <v>5</v>
+      </c>
+      <c r="G18" s="11">
+        <v>5</v>
+      </c>
+      <c r="H18" s="11">
         <v>3</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="11">
         <v>4.5</v>
       </c>
-      <c r="J18" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L18" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N18" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O18" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P18" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q18" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R18" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S18" s="11" t="s">
+      <c r="J18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S18" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8691,58 +11622,58 @@
       <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="11">
         <v>3</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="7">
         <v>4.33</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="7">
         <v>4.33</v>
       </c>
-      <c r="F19" s="8">
-        <v>5</v>
-      </c>
-      <c r="G19" s="8">
-        <v>5</v>
-      </c>
-      <c r="H19" s="8">
+      <c r="F19" s="11">
+        <v>5</v>
+      </c>
+      <c r="G19" s="11">
+        <v>5</v>
+      </c>
+      <c r="H19" s="11">
         <v>3</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="11">
         <v>3</v>
       </c>
-      <c r="J19" s="8">
-        <v>5</v>
-      </c>
-      <c r="K19" s="8">
-        <v>5</v>
-      </c>
-      <c r="L19" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N19" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O19" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P19" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q19" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R19" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S19" s="11" t="s">
+      <c r="J19" s="11">
+        <v>5</v>
+      </c>
+      <c r="K19" s="11">
+        <v>5</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N19" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O19" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P19" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q19" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R19" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S19" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8750,58 +11681,58 @@
       <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="11">
         <v>3</v>
       </c>
-      <c r="D20" s="9">
-        <v>5</v>
-      </c>
-      <c r="E20" s="9">
+      <c r="D20" s="7">
+        <v>5</v>
+      </c>
+      <c r="E20" s="7">
         <v>4.17</v>
       </c>
-      <c r="F20" s="8">
-        <v>5</v>
-      </c>
-      <c r="G20" s="8">
+      <c r="F20" s="11">
+        <v>5</v>
+      </c>
+      <c r="G20" s="11">
         <v>4</v>
       </c>
-      <c r="H20" s="8">
-        <v>5</v>
-      </c>
-      <c r="I20" s="8">
+      <c r="H20" s="11">
+        <v>5</v>
+      </c>
+      <c r="I20" s="11">
         <v>4</v>
       </c>
-      <c r="J20" s="8">
-        <v>5</v>
-      </c>
-      <c r="K20" s="8">
+      <c r="J20" s="11">
+        <v>5</v>
+      </c>
+      <c r="K20" s="11">
         <v>4.5</v>
       </c>
-      <c r="L20" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P20" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q20" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R20" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S20" s="11" t="s">
+      <c r="L20" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P20" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q20" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R20" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S20" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8809,58 +11740,58 @@
       <c r="A21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="11">
         <v>1</v>
       </c>
-      <c r="D21" s="9">
-        <v>5</v>
-      </c>
-      <c r="E21" s="9">
+      <c r="D21" s="7">
+        <v>5</v>
+      </c>
+      <c r="E21" s="7">
         <v>4</v>
       </c>
-      <c r="F21" s="8">
-        <v>5</v>
-      </c>
-      <c r="G21" s="8">
+      <c r="F21" s="11">
+        <v>5</v>
+      </c>
+      <c r="G21" s="11">
         <v>4</v>
       </c>
-      <c r="H21" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P21" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q21" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R21" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S21" s="11" t="s">
+      <c r="H21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S21" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8868,58 +11799,58 @@
       <c r="A22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="11">
         <v>2</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="7">
         <v>4.25</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="7">
         <v>4.75</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="11">
         <v>4</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="11">
         <v>4.5</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="11">
         <v>4.5</v>
       </c>
-      <c r="I22" s="8">
-        <v>5</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L22" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N22" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O22" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P22" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q22" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R22" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S22" s="11" t="s">
+      <c r="I22" s="11">
+        <v>5</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N22" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O22" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P22" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q22" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R22" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S22" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8927,58 +11858,58 @@
       <c r="A23" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="11">
         <v>2</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="7">
         <v>4.25</v>
       </c>
-      <c r="E23" s="9">
-        <v>5</v>
-      </c>
-      <c r="F23" s="8">
+      <c r="E23" s="7">
+        <v>5</v>
+      </c>
+      <c r="F23" s="11">
         <v>4</v>
       </c>
-      <c r="G23" s="8">
-        <v>5</v>
-      </c>
-      <c r="H23" s="8">
+      <c r="G23" s="11">
+        <v>5</v>
+      </c>
+      <c r="H23" s="11">
         <v>4.5</v>
       </c>
-      <c r="I23" s="8">
-        <v>5</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N23" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P23" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q23" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R23" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S23" s="11" t="s">
+      <c r="I23" s="11">
+        <v>5</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O23" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P23" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q23" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R23" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S23" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8986,58 +11917,58 @@
       <c r="A24" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="11">
         <v>2</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="7">
         <v>4.25</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="7">
         <v>4</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="11">
         <v>4</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="11">
         <v>4.5</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="11">
         <v>4.5</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="11">
         <v>3.5</v>
       </c>
-      <c r="J24" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L24" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N24" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P24" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q24" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R24" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S24" s="11" t="s">
+      <c r="J24" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N24" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O24" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P24" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q24" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R24" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S24" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9045,58 +11976,58 @@
       <c r="A25" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="11">
         <v>2</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="7">
         <v>4.5</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="7">
         <v>4.75</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="11">
         <v>4.5</v>
       </c>
-      <c r="G25" s="8">
-        <v>5</v>
-      </c>
-      <c r="H25" s="8">
+      <c r="G25" s="11">
+        <v>5</v>
+      </c>
+      <c r="H25" s="11">
         <v>4.5</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="11">
         <v>4.5</v>
       </c>
-      <c r="J25" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L25" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N25" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P25" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q25" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R25" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S25" s="11" t="s">
+      <c r="J25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S25" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9104,58 +12035,58 @@
       <c r="A26" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="11">
         <v>2</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="7">
         <v>4.5</v>
       </c>
-      <c r="E26" s="9">
-        <v>5</v>
-      </c>
-      <c r="F26" s="8">
+      <c r="E26" s="7">
+        <v>5</v>
+      </c>
+      <c r="F26" s="11">
         <v>4.5</v>
       </c>
-      <c r="G26" s="8">
-        <v>5</v>
-      </c>
-      <c r="H26" s="8">
+      <c r="G26" s="11">
+        <v>5</v>
+      </c>
+      <c r="H26" s="11">
         <v>4.5</v>
       </c>
-      <c r="I26" s="8">
-        <v>5</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K26" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L26" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N26" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P26" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q26" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R26" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S26" s="11" t="s">
+      <c r="I26" s="11">
+        <v>5</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S26" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9163,58 +12094,58 @@
       <c r="A27" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="11">
         <v>2</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="7">
         <v>4.5</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="7">
         <v>4.5</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="11">
         <v>4.5</v>
       </c>
-      <c r="G27" s="8">
-        <v>5</v>
-      </c>
-      <c r="H27" s="8">
+      <c r="G27" s="11">
+        <v>5</v>
+      </c>
+      <c r="H27" s="11">
         <v>4.5</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="11">
         <v>4</v>
       </c>
-      <c r="J27" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K27" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L27" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N27" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P27" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q27" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R27" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S27" s="11" t="s">
+      <c r="J27" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N27" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O27" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P27" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q27" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R27" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S27" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9222,58 +12153,58 @@
       <c r="A28" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="11">
         <v>2</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="7">
         <v>4.5</v>
       </c>
-      <c r="E28" s="9">
-        <v>5</v>
-      </c>
-      <c r="F28" s="8">
+      <c r="E28" s="7">
+        <v>5</v>
+      </c>
+      <c r="F28" s="11">
         <v>4.5</v>
       </c>
-      <c r="G28" s="8">
-        <v>5</v>
-      </c>
-      <c r="H28" s="8">
+      <c r="G28" s="11">
+        <v>5</v>
+      </c>
+      <c r="H28" s="11">
         <v>4.5</v>
       </c>
-      <c r="I28" s="8">
-        <v>5</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K28" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L28" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M28" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N28" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O28" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P28" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q28" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R28" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S28" s="11" t="s">
+      <c r="I28" s="11">
+        <v>5</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N28" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O28" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P28" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q28" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R28" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S28" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9281,58 +12212,58 @@
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="11">
         <v>2</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="7">
         <v>4.5</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="7">
         <v>4</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="11">
         <v>4.5</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="11">
         <v>4</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="11">
         <v>4.5</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="11">
         <v>4</v>
       </c>
-      <c r="J29" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L29" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N29" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O29" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P29" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q29" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R29" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S29" s="11" t="s">
+      <c r="J29" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N29" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O29" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P29" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q29" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R29" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S29" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9340,58 +12271,58 @@
       <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="11">
         <v>7</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="7">
         <v>4.5</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="7">
         <v>3.71</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="11">
         <v>4.5</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="11">
         <v>3.5</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="11">
         <v>4.5</v>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="11">
         <v>4</v>
       </c>
-      <c r="J30" s="8">
+      <c r="J30" s="11">
         <v>4.5</v>
       </c>
-      <c r="K30" s="8">
+      <c r="K30" s="11">
         <v>2</v>
       </c>
-      <c r="L30" s="8">
+      <c r="L30" s="11">
         <v>4.5</v>
       </c>
-      <c r="M30" s="8">
+      <c r="M30" s="11">
         <v>4</v>
       </c>
-      <c r="N30" s="8">
+      <c r="N30" s="11">
         <v>4.5</v>
       </c>
-      <c r="O30" s="8">
+      <c r="O30" s="11">
         <v>3.5</v>
       </c>
-      <c r="P30" s="8">
+      <c r="P30" s="11">
         <v>4.5</v>
       </c>
-      <c r="Q30" s="8">
+      <c r="Q30" s="11">
         <v>4</v>
       </c>
-      <c r="R30" s="8">
+      <c r="R30" s="11">
         <v>4.5</v>
       </c>
-      <c r="S30" s="8">
+      <c r="S30" s="11">
         <v>5</v>
       </c>
     </row>
@@ -9399,58 +12330,58 @@
       <c r="A31" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="11">
         <v>3</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="7">
         <v>4.5</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="7">
         <v>3.5</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="11">
         <v>4.5</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="11">
         <v>2</v>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="11">
         <v>4.5</v>
       </c>
-      <c r="I31" s="8">
+      <c r="I31" s="11">
         <v>4.5</v>
       </c>
-      <c r="J31" s="8">
+      <c r="J31" s="11">
         <v>4.5</v>
       </c>
-      <c r="K31" s="8">
+      <c r="K31" s="11">
         <v>4</v>
       </c>
-      <c r="L31" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M31" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N31" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O31" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P31" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q31" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R31" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S31" s="11" t="s">
+      <c r="L31" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N31" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O31" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P31" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q31" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R31" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S31" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9475,43 +12406,43 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:13">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="7" t="s">
+      <c r="F1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9519,40 +12450,40 @@
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="7">
         <v>4.33</v>
       </c>
-      <c r="E2" s="9">
-        <v>5</v>
-      </c>
-      <c r="F2" s="8">
+      <c r="E2" s="7">
+        <v>5</v>
+      </c>
+      <c r="F2" s="11">
         <v>3.5</v>
       </c>
-      <c r="G2" s="8">
-        <v>5</v>
-      </c>
-      <c r="H2" s="8">
+      <c r="G2" s="11">
+        <v>5</v>
+      </c>
+      <c r="H2" s="11">
         <v>4.5</v>
       </c>
-      <c r="I2" s="8">
-        <v>5</v>
-      </c>
-      <c r="J2" s="8">
-        <v>5</v>
-      </c>
-      <c r="K2" s="8">
-        <v>5</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="11" t="s">
+      <c r="I2" s="11">
+        <v>5</v>
+      </c>
+      <c r="J2" s="11">
+        <v>5</v>
+      </c>
+      <c r="K2" s="11">
+        <v>5</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9560,40 +12491,40 @@
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="11">
         <v>1</v>
       </c>
-      <c r="D3" s="9">
-        <v>5</v>
-      </c>
-      <c r="E3" s="9">
+      <c r="D3" s="7">
+        <v>5</v>
+      </c>
+      <c r="E3" s="7">
         <v>4.5</v>
       </c>
-      <c r="F3" s="8">
-        <v>5</v>
-      </c>
-      <c r="G3" s="8">
+      <c r="F3" s="11">
+        <v>5</v>
+      </c>
+      <c r="G3" s="11">
         <v>4.5</v>
       </c>
-      <c r="H3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="11" t="s">
+      <c r="H3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9601,40 +12532,40 @@
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="11">
         <v>1</v>
       </c>
-      <c r="D4" s="9">
-        <v>5</v>
-      </c>
-      <c r="E4" s="9">
-        <v>5</v>
-      </c>
-      <c r="F4" s="8">
-        <v>5</v>
-      </c>
-      <c r="G4" s="8">
-        <v>5</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" s="11" t="s">
+      <c r="D4" s="7">
+        <v>5</v>
+      </c>
+      <c r="E4" s="7">
+        <v>5</v>
+      </c>
+      <c r="F4" s="11">
+        <v>5</v>
+      </c>
+      <c r="G4" s="11">
+        <v>5</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9642,40 +12573,40 @@
       <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="11">
         <v>3</v>
       </c>
-      <c r="D5" s="9">
-        <v>5</v>
-      </c>
-      <c r="E5" s="9">
-        <v>5</v>
-      </c>
-      <c r="F5" s="8">
-        <v>5</v>
-      </c>
-      <c r="G5" s="8">
-        <v>5</v>
-      </c>
-      <c r="H5" s="8">
-        <v>5</v>
-      </c>
-      <c r="I5" s="8">
-        <v>5</v>
-      </c>
-      <c r="J5" s="8">
-        <v>5</v>
-      </c>
-      <c r="K5" s="8">
-        <v>5</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="11" t="s">
+      <c r="D5" s="7">
+        <v>5</v>
+      </c>
+      <c r="E5" s="7">
+        <v>5</v>
+      </c>
+      <c r="F5" s="11">
+        <v>5</v>
+      </c>
+      <c r="G5" s="11">
+        <v>5</v>
+      </c>
+      <c r="H5" s="11">
+        <v>5</v>
+      </c>
+      <c r="I5" s="11">
+        <v>5</v>
+      </c>
+      <c r="J5" s="11">
+        <v>5</v>
+      </c>
+      <c r="K5" s="11">
+        <v>5</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9683,40 +12614,40 @@
       <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="11">
         <v>2</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="7">
         <v>4.5</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="7">
         <v>3.75</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="11">
         <v>4</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="11">
         <v>3</v>
       </c>
-      <c r="H6" s="8">
-        <v>5</v>
-      </c>
-      <c r="I6" s="8">
+      <c r="H6" s="11">
+        <v>5</v>
+      </c>
+      <c r="I6" s="11">
         <v>4.5</v>
       </c>
-      <c r="J6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="11" t="s">
+      <c r="J6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9724,40 +12655,40 @@
       <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="11">
         <v>1</v>
       </c>
-      <c r="D7" s="9">
-        <v>5</v>
-      </c>
-      <c r="E7" s="9">
-        <v>5</v>
-      </c>
-      <c r="F7" s="8">
-        <v>5</v>
-      </c>
-      <c r="G7" s="8">
-        <v>5</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="11" t="s">
+      <c r="D7" s="7">
+        <v>5</v>
+      </c>
+      <c r="E7" s="7">
+        <v>5</v>
+      </c>
+      <c r="F7" s="11">
+        <v>5</v>
+      </c>
+      <c r="G7" s="11">
+        <v>5</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9765,40 +12696,40 @@
       <c r="A8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="11">
         <v>4</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="7">
         <v>4.5</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="7">
         <v>4.12</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="11">
         <v>4</v>
       </c>
-      <c r="G8" s="8">
-        <v>5</v>
-      </c>
-      <c r="H8" s="8">
+      <c r="G8" s="11">
+        <v>5</v>
+      </c>
+      <c r="H8" s="11">
         <v>4</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="11">
         <v>3</v>
       </c>
-      <c r="J8" s="8">
-        <v>5</v>
-      </c>
-      <c r="K8" s="8">
+      <c r="J8" s="11">
+        <v>5</v>
+      </c>
+      <c r="K8" s="11">
         <v>4</v>
       </c>
-      <c r="L8" s="8">
-        <v>5</v>
-      </c>
-      <c r="M8" s="8">
+      <c r="L8" s="11">
+        <v>5</v>
+      </c>
+      <c r="M8" s="11">
         <v>4.5</v>
       </c>
     </row>
@@ -9806,40 +12737,40 @@
       <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="11">
         <v>1</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="7">
         <v>4</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="7">
         <v>4.5</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="11">
         <v>4</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="11">
         <v>4.5</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="11" t="s">
+      <c r="H9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9847,40 +12778,40 @@
       <c r="A10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="11">
         <v>2</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="7">
         <v>4</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="7">
         <v>4</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="11">
         <v>4</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="11">
         <v>3</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="11">
         <v>4</v>
       </c>
-      <c r="I10" s="8">
-        <v>5</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="11" t="s">
+      <c r="I10" s="11">
+        <v>5</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9894,7 +12825,392 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <sheetData>
+    <row r="1" ht="27.6" spans="1:9">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="9">
+        <v>2</v>
+      </c>
+      <c r="D2" s="7">
+        <v>5</v>
+      </c>
+      <c r="E2" s="7">
+        <v>4.25</v>
+      </c>
+      <c r="F2" s="9">
+        <v>5</v>
+      </c>
+      <c r="G2" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="H2" s="9">
+        <v>5</v>
+      </c>
+      <c r="I2" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="9">
+        <v>2</v>
+      </c>
+      <c r="D3" s="7">
+        <v>5</v>
+      </c>
+      <c r="E3" s="7">
+        <v>4.25</v>
+      </c>
+      <c r="F3" s="9">
+        <v>5</v>
+      </c>
+      <c r="G3" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="H3" s="9">
+        <v>5</v>
+      </c>
+      <c r="I3" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="9">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7">
+        <v>4</v>
+      </c>
+      <c r="E4" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="F4" s="9">
+        <v>4</v>
+      </c>
+      <c r="G4" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="6"/>
+  <sheetData>
+    <row r="1" ht="27.6" spans="1:11">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="9">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7">
+        <v>5</v>
+      </c>
+      <c r="E2" s="7">
+        <v>5</v>
+      </c>
+      <c r="F2" s="9">
+        <v>5</v>
+      </c>
+      <c r="G2" s="9">
+        <v>5</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="9">
+        <v>3</v>
+      </c>
+      <c r="D3" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="E3" s="7">
+        <v>3.17</v>
+      </c>
+      <c r="F3" s="9">
+        <v>5</v>
+      </c>
+      <c r="G3" s="9">
+        <v>5</v>
+      </c>
+      <c r="H3" s="9">
+        <v>5</v>
+      </c>
+      <c r="I3" s="9">
+        <v>0</v>
+      </c>
+      <c r="J3" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="K3" s="9">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="9">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7">
+        <v>5</v>
+      </c>
+      <c r="E4" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="F4" s="9">
+        <v>5</v>
+      </c>
+      <c r="G4" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="9">
+        <v>2</v>
+      </c>
+      <c r="D5" s="7">
+        <v>5</v>
+      </c>
+      <c r="E5" s="7">
+        <v>4.75</v>
+      </c>
+      <c r="F5" s="9">
+        <v>5</v>
+      </c>
+      <c r="G5" s="9">
+        <v>5</v>
+      </c>
+      <c r="H5" s="9">
+        <v>5</v>
+      </c>
+      <c r="I5" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="9">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7">
+        <v>4</v>
+      </c>
+      <c r="E6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="F6" s="9">
+        <v>4</v>
+      </c>
+      <c r="G6" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="9">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7">
+        <v>4</v>
+      </c>
+      <c r="E7" s="7">
+        <v>4</v>
+      </c>
+      <c r="F7" s="9">
+        <v>4</v>
+      </c>
+      <c r="G7" s="9">
+        <v>4</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultColWidth="8.67592592592593" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -9907,39 +13223,39 @@
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:7">
-      <c r="A1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>39</v>
+      <c r="E1" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="6" t="s">
-        <v>40</v>
+      <c r="A2" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="12">
         <v>2</v>
       </c>
       <c r="E2" s="5">
@@ -9953,16 +13269,16 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="6" t="s">
-        <v>40</v>
+      <c r="A3" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="12">
         <v>2</v>
       </c>
       <c r="E3" s="5">
@@ -9976,16 +13292,16 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="6" t="s">
-        <v>40</v>
+      <c r="A4" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="12">
         <v>2</v>
       </c>
       <c r="E4" s="5">
@@ -9999,16 +13315,16 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="6" t="s">
-        <v>40</v>
+      <c r="A5" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="12">
         <v>2</v>
       </c>
       <c r="E5" s="5">
@@ -10022,16 +13338,16 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="6" t="s">
-        <v>40</v>
+      <c r="A6" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="12">
         <v>2</v>
       </c>
       <c r="E6" s="5">
@@ -10045,16 +13361,16 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="6" t="s">
-        <v>40</v>
+      <c r="A7" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="12">
         <v>2</v>
       </c>
       <c r="E7" s="5">
@@ -10068,16 +13384,16 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="6" t="s">
-        <v>40</v>
+      <c r="A8" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="12">
         <v>2</v>
       </c>
       <c r="E8" s="5">
@@ -10091,16 +13407,16 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="6" t="s">
-        <v>40</v>
+      <c r="A9" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="12">
         <v>2</v>
       </c>
       <c r="E9" s="5">
@@ -10114,16 +13430,16 @@
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="6" t="s">
-        <v>40</v>
+      <c r="A10" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="12">
         <v>3</v>
       </c>
       <c r="E10" s="5">
@@ -10137,16 +13453,16 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="6" t="s">
-        <v>40</v>
+      <c r="A11" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="12">
         <v>3</v>
       </c>
       <c r="E11" s="5">
@@ -10160,16 +13476,16 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="6" t="s">
-        <v>40</v>
+      <c r="A12" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="12">
         <v>2</v>
       </c>
       <c r="E12" s="5">
@@ -10183,16 +13499,16 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="6" t="s">
-        <v>40</v>
+      <c r="A13" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="12">
         <v>2</v>
       </c>
       <c r="E13" s="5">
@@ -10206,16 +13522,16 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="6" t="s">
-        <v>40</v>
+      <c r="A14" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="12">
         <v>2</v>
       </c>
       <c r="E14" s="5">
@@ -10229,16 +13545,16 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="6" t="s">
-        <v>40</v>
+      <c r="A15" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="12">
         <v>2</v>
       </c>
       <c r="E15" s="5">
@@ -10252,16 +13568,16 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="6" t="s">
-        <v>40</v>
+      <c r="A16" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="12">
         <v>2</v>
       </c>
       <c r="E16" s="5">
@@ -10275,16 +13591,16 @@
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="6" t="s">
-        <v>40</v>
+      <c r="A17" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="12">
         <v>2</v>
       </c>
       <c r="E17" s="5">
@@ -10298,16 +13614,16 @@
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="6" t="s">
-        <v>40</v>
+      <c r="A18" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="12">
         <v>2</v>
       </c>
       <c r="E18" s="5">
@@ -10321,16 +13637,16 @@
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="6" t="s">
-        <v>40</v>
+      <c r="A19" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="12">
         <v>3</v>
       </c>
       <c r="E19" s="5">
@@ -10344,16 +13660,16 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="6" t="s">
-        <v>40</v>
+      <c r="A20" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="12">
         <v>3</v>
       </c>
       <c r="E20" s="5">
@@ -10367,16 +13683,16 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="6" t="s">
-        <v>40</v>
+      <c r="A21" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="12">
         <v>1</v>
       </c>
       <c r="E21" s="5">
@@ -10390,16 +13706,16 @@
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="6" t="s">
-        <v>40</v>
+      <c r="A22" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="12">
         <v>2</v>
       </c>
       <c r="E22" s="5">
@@ -10413,16 +13729,16 @@
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="6" t="s">
-        <v>40</v>
+      <c r="A23" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="12">
         <v>2</v>
       </c>
       <c r="E23" s="5">
@@ -10436,16 +13752,16 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="6" t="s">
-        <v>40</v>
+      <c r="A24" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="12">
         <v>2</v>
       </c>
       <c r="E24" s="5">
@@ -10459,16 +13775,16 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="6" t="s">
-        <v>40</v>
+      <c r="A25" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="12">
         <v>2</v>
       </c>
       <c r="E25" s="5">
@@ -10482,16 +13798,16 @@
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="6" t="s">
-        <v>40</v>
+      <c r="A26" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="12">
         <v>2</v>
       </c>
       <c r="E26" s="5">
@@ -10505,16 +13821,16 @@
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="6" t="s">
-        <v>40</v>
+      <c r="A27" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="12">
         <v>2</v>
       </c>
       <c r="E27" s="5">
@@ -10528,16 +13844,16 @@
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="6" t="s">
-        <v>40</v>
+      <c r="A28" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="12">
         <v>2</v>
       </c>
       <c r="E28" s="5">
@@ -10551,16 +13867,16 @@
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
+      <c r="A29" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="12">
         <v>2</v>
       </c>
       <c r="E29" s="5">
@@ -10574,16 +13890,16 @@
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="6" t="s">
-        <v>40</v>
+      <c r="A30" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="12">
         <v>7</v>
       </c>
       <c r="E30" s="5">
@@ -10597,16 +13913,16 @@
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="6" t="s">
-        <v>40</v>
+      <c r="A31" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="12">
         <v>3</v>
       </c>
       <c r="E31" s="5">
@@ -10620,16 +13936,16 @@
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="6" t="s">
-        <v>41</v>
+      <c r="A32" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="12">
         <v>3</v>
       </c>
       <c r="E32" s="5">
@@ -10643,16 +13959,16 @@
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="6" t="s">
-        <v>41</v>
+      <c r="A33" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="12">
         <v>1</v>
       </c>
       <c r="E33" s="5">
@@ -10666,16 +13982,16 @@
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="6" t="s">
-        <v>41</v>
+      <c r="A34" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="12">
         <v>1</v>
       </c>
       <c r="E34" s="5">
@@ -10689,16 +14005,16 @@
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="6" t="s">
-        <v>41</v>
+      <c r="A35" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="12">
         <v>3</v>
       </c>
       <c r="E35" s="5">
@@ -10712,16 +14028,16 @@
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="6" t="s">
-        <v>41</v>
+      <c r="A36" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="12">
         <v>2</v>
       </c>
       <c r="E36" s="5">
@@ -10735,16 +14051,16 @@
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="6" t="s">
-        <v>41</v>
+      <c r="A37" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="12">
         <v>1</v>
       </c>
       <c r="E37" s="5">
@@ -10758,16 +14074,16 @@
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="6" t="s">
-        <v>41</v>
+      <c r="A38" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="12">
         <v>4</v>
       </c>
       <c r="E38" s="5">
@@ -10781,16 +14097,16 @@
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="6" t="s">
-        <v>41</v>
+      <c r="A39" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="12">
         <v>1</v>
       </c>
       <c r="E39" s="5">
@@ -10804,16 +14120,16 @@
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="6" t="s">
-        <v>41</v>
+      <c r="A40" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="12">
         <v>2</v>
       </c>
       <c r="E40" s="5">
@@ -10823,6 +14139,213 @@
         <v>4</v>
       </c>
       <c r="G40" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D41" s="9">
+        <v>2</v>
+      </c>
+      <c r="E41" s="7">
+        <v>5</v>
+      </c>
+      <c r="F41" s="7">
+        <v>4.25</v>
+      </c>
+      <c r="G41" s="7">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D42" s="9">
+        <v>2</v>
+      </c>
+      <c r="E42" s="7">
+        <v>5</v>
+      </c>
+      <c r="F42" s="7">
+        <v>4.25</v>
+      </c>
+      <c r="G42" s="7">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D43" s="9">
+        <v>1</v>
+      </c>
+      <c r="E43" s="7">
+        <v>4</v>
+      </c>
+      <c r="F43" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="G43" s="7">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44" s="9">
+        <v>1</v>
+      </c>
+      <c r="E44" s="7">
+        <v>5</v>
+      </c>
+      <c r="F44" s="7">
+        <v>5</v>
+      </c>
+      <c r="G44" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" s="9">
+        <v>3</v>
+      </c>
+      <c r="E45" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="F45" s="7">
+        <v>3.17</v>
+      </c>
+      <c r="G45" s="7">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" s="9">
+        <v>1</v>
+      </c>
+      <c r="E46" s="7">
+        <v>5</v>
+      </c>
+      <c r="F46" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="G46" s="7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D47" s="9">
+        <v>2</v>
+      </c>
+      <c r="E47" s="7">
+        <v>5</v>
+      </c>
+      <c r="F47" s="7">
+        <v>4.75</v>
+      </c>
+      <c r="G47" s="7">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="9">
+        <v>1</v>
+      </c>
+      <c r="E48" s="7">
+        <v>4</v>
+      </c>
+      <c r="F48" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="G48" s="7">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D49" s="9">
+        <v>1</v>
+      </c>
+      <c r="E49" s="7">
+        <v>4</v>
+      </c>
+      <c r="F49" s="7">
+        <v>4</v>
+      </c>
+      <c r="G49" s="7">
         <v>4</v>
       </c>
     </row>
@@ -10833,11 +14356,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="8.67592592592593" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="8.67592592592593" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -10848,143 +14371,263 @@
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:6">
-      <c r="A1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>45</v>
+      <c r="C1" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="8" t="s">
-        <v>40</v>
+      <c r="A2" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="11">
         <v>22</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="7">
         <v>4.89</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="7">
         <v>4.36</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="7">
         <v>4.62</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="8" t="s">
-        <v>40</v>
+      <c r="A3" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="8">
-        <v>21</v>
-      </c>
-      <c r="D3" s="9">
+      <c r="C3" s="11">
+        <v>21</v>
+      </c>
+      <c r="D3" s="7">
         <v>4.55</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="7">
         <v>4.52</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="7">
         <v>4.54</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="8" t="s">
-        <v>40</v>
+      <c r="A4" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="11">
         <v>26</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="7">
         <v>4.44</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="7">
         <v>4.25</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="7">
         <v>4.35</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="8" t="s">
-        <v>41</v>
+      <c r="A5" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="8">
-        <v>5</v>
-      </c>
-      <c r="D5" s="9">
+      <c r="C5" s="11">
+        <v>5</v>
+      </c>
+      <c r="D5" s="7">
         <v>4.6</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="7">
         <v>4.9</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="7">
         <v>4.75</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="8" t="s">
-        <v>41</v>
+      <c r="A6" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="11">
         <v>6</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="7">
         <v>4.83</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="7">
         <v>4.58</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="7">
         <v>4.71</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="8" t="s">
-        <v>41</v>
+      <c r="A7" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="11">
         <v>7</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="7">
         <v>4.29</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="7">
         <v>4.14</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="7">
         <v>4.21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="9">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7">
+        <v>5</v>
+      </c>
+      <c r="E8" s="7">
+        <v>4.25</v>
+      </c>
+      <c r="F8" s="7">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="9">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7">
+        <v>5</v>
+      </c>
+      <c r="E9" s="7">
+        <v>4.25</v>
+      </c>
+      <c r="F9" s="7">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="9">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7">
+        <v>4</v>
+      </c>
+      <c r="E10" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="F10" s="7">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="9">
+        <v>4</v>
+      </c>
+      <c r="D11" s="7">
+        <v>4.62</v>
+      </c>
+      <c r="E11" s="7">
+        <v>3.62</v>
+      </c>
+      <c r="F11" s="7">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="9">
+        <v>3</v>
+      </c>
+      <c r="D12" s="7">
+        <v>5</v>
+      </c>
+      <c r="E12" s="7">
+        <v>4.67</v>
+      </c>
+      <c r="F12" s="7">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="9">
+        <v>2</v>
+      </c>
+      <c r="D13" s="7">
+        <v>4</v>
+      </c>
+      <c r="E13" s="7">
+        <v>4.25</v>
+      </c>
+      <c r="F13" s="7">
+        <v>4.12</v>
       </c>
     </row>
   </sheetData>
@@ -10995,10 +14638,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:E14"/>
+  <dimension ref="B1:E17"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="2:5">
@@ -11016,13 +14659,13 @@
       <c r="B2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="8">
         <v>2</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="8">
         <v>2</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="8">
         <v>2</v>
       </c>
     </row>
@@ -11030,13 +14673,13 @@
       <c r="B3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="8">
         <v>2</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="8">
         <v>2</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="8">
         <v>2</v>
       </c>
     </row>
@@ -11044,13 +14687,13 @@
       <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="8">
         <v>2</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="8">
         <v>2</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="8">
         <v>2</v>
       </c>
     </row>
@@ -11058,13 +14701,13 @@
       <c r="B5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="8">
         <v>2</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="8">
         <v>2</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="8">
         <v>2</v>
       </c>
     </row>
@@ -11072,13 +14715,13 @@
       <c r="B6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="8">
         <v>2</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="8">
         <v>2</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="8">
         <v>2</v>
       </c>
     </row>
@@ -11086,13 +14729,13 @@
       <c r="B7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="8">
         <v>2</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="8">
         <v>2</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="8">
         <v>2</v>
       </c>
     </row>
@@ -11100,13 +14743,13 @@
       <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="8">
         <v>2</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="8">
         <v>2</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="8">
         <v>2</v>
       </c>
     </row>
@@ -11114,13 +14757,13 @@
       <c r="B9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="8">
         <v>2</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="8">
         <v>3</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="8">
         <v>2</v>
       </c>
     </row>
@@ -11128,13 +14771,13 @@
       <c r="B10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="8">
         <v>3</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="8">
         <v>3</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="8">
         <v>7</v>
       </c>
     </row>
@@ -11142,13 +14785,13 @@
       <c r="B11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="8">
         <v>3</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="8">
         <v>1</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="8">
         <v>3</v>
       </c>
     </row>
@@ -11156,13 +14799,13 @@
       <c r="B12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="8">
         <v>3</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="8">
         <v>3</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="8">
         <v>4</v>
       </c>
     </row>
@@ -11170,13 +14813,13 @@
       <c r="B13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="8">
         <v>1</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="8">
         <v>2</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="8">
         <v>1</v>
       </c>
     </row>
@@ -11184,14 +14827,56 @@
       <c r="B14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="8">
         <v>1</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="8">
         <v>1</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="8">
         <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="B15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="9">
+        <v>2</v>
+      </c>
+      <c r="D15" s="9">
+        <v>2</v>
+      </c>
+      <c r="E15" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="B16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="9">
+        <v>1</v>
+      </c>
+      <c r="D16" s="9">
+        <v>1</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="9">
+        <v>3</v>
+      </c>
+      <c r="D17" s="9">
+        <v>2</v>
+      </c>
+      <c r="E17" s="9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -11201,10 +14886,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:F14"/>
+  <dimension ref="C1:F17"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="3:6">
@@ -11397,6 +15082,48 @@
         <v>5</v>
       </c>
       <c r="F14" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="3:6">
+      <c r="C15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="7">
+        <v>4.62</v>
+      </c>
+      <c r="E15" s="7">
+        <v>4.62</v>
+      </c>
+      <c r="F15" s="7">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="16" spans="3:6">
+      <c r="C16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="7">
+        <v>5</v>
+      </c>
+      <c r="E16" s="7">
+        <v>4.75</v>
+      </c>
+      <c r="F16" s="7">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6">
+      <c r="C17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="7">
+        <v>3.83</v>
+      </c>
+      <c r="E17" s="7">
+        <v>4.88</v>
+      </c>
+      <c r="F17" s="7">
         <v>4</v>
       </c>
     </row>
